--- a/Day 01.xlsx
+++ b/Day 01.xlsx
@@ -9,12 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Lesson 01" sheetId="1" r:id="rId1"/>
     <sheet name="Lesson 02" sheetId="2" r:id="rId2"/>
+    <sheet name="Lesson 07" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Lesson 07'!$A$1:$C$11</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
   <si>
     <t>Alex</t>
   </si>
@@ -76,13 +80,61 @@
   </si>
   <si>
     <t>Performance</t>
+  </si>
+  <si>
+    <t>My Shop Sales Report — Week 1</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Apples</t>
+  </si>
+  <si>
+    <t>Mangoes</t>
+  </si>
+  <si>
+    <t>Milk</t>
+  </si>
+  <si>
+    <t>Cheese</t>
+  </si>
+  <si>
+    <t>Bread</t>
+  </si>
+  <si>
+    <t>Cake</t>
+  </si>
+  <si>
+    <t>Yogurt</t>
+  </si>
+  <si>
+    <t>Bananas</t>
+  </si>
+  <si>
+    <t>Croissant</t>
+  </si>
+  <si>
+    <t>Butter</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Dairy</t>
+  </si>
+  <si>
+    <t>Bakery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,16 +142,64 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -107,14 +207,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,169 +592,551 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="4">
         <v>3000</v>
       </c>
-      <c r="C2" t="str">
-        <f>IF(B2&gt;2000,"Good Day","Bad Day")</f>
+      <c r="C3" s="4" t="str">
+        <f>IF(B3&gt;2000,"Good Day","Bad Day")</f>
         <v>Good Day</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <f>100+200</f>
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="2">
         <v>2300</v>
       </c>
-      <c r="C3" t="str">
-        <f t="shared" ref="C3:C7" si="0">IF(B3&gt;2000,"Good Day","Bad Day")</f>
+      <c r="C4" s="2" t="str">
+        <f>IF(B4&gt;2000,"Good Day","Bad Day")</f>
         <v>Good Day</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <f>500-150</f>
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="4">
         <v>1800</v>
       </c>
-      <c r="C4" t="str">
-        <f t="shared" si="0"/>
+      <c r="C5" s="4" t="str">
+        <f>IF(B5&gt;2000,"Good Day","Bad Day")</f>
         <v>Bad Day</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <f>50*4</f>
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="2">
         <v>3100</v>
       </c>
-      <c r="C5" t="str">
-        <f t="shared" si="0"/>
+      <c r="C6" s="2" t="str">
+        <f>IF(B6&gt;2000,"Good Day","Bad Day")</f>
         <v>Good Day</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <f>100/4</f>
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B7" s="4">
         <v>2750</v>
       </c>
-      <c r="C6" t="str">
-        <f t="shared" si="0"/>
-        <v>Good Day</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>4200</v>
-      </c>
-      <c r="C7" t="str">
-        <f t="shared" si="0"/>
+      <c r="C7" s="4" t="str">
+        <f>IF(B7&gt;2000,"Good Day","Bad Day")</f>
         <v>Good Day</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>4200</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f>IF(B8&gt;2000,"Good Day","Bad Day")</f>
+        <v>Good Day</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <f>SUM(B2:B7)</f>
+      <c r="B9" s="9">
+        <f>SUM(B3:B8)</f>
         <v>17150</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
-        <f>AVERAGE(B2:B7)</f>
+      <c r="B10" s="9">
+        <f>AVERAGE(B3:B8)</f>
         <v>2858.3333333333335</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <f>MAX(B2:B7)</f>
+      <c r="B11" s="9">
+        <f>MAX(B3:B8)</f>
         <v>4200</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
-        <f>MIN(B2:B7)</f>
+      <c r="B12" s="9">
+        <f>MIN(B3:B8)</f>
         <v>1800</v>
       </c>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
-        <f>COUNT(B2:B7)</f>
+      <c r="B14" s="2">
+        <f>COUNT(B3:B8)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
-        <f>COUNTA(A2:A7)</f>
+      <c r="B15" s="2">
+        <f>COUNTA(A3:A8)</f>
         <v>6</v>
       </c>
+      <c r="C15" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="10">
+        <v>1500</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2700</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="10">
+        <v>950</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="2">
+        <v>650</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="10">
+        <v>3800</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2100</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="10">
+        <v>1800</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3200</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="10">
+        <v>800</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1200</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="10">
+        <v>1500</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2700</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="10">
+        <v>950</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2">
+        <v>650</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="10">
+        <v>3800</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2100</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="10">
+        <v>1800</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2">
+        <v>3200</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="10">
+        <v>800</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1200</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10">
+        <v>1500</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2700</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="10">
+        <v>950</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="2">
+        <v>650</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10">
+        <v>3800</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2100</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="10">
+        <v>1800</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="2">
+        <v>3200</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="10">
+        <v>800</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="2">
+        <v>1200</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:C11">
+    <sortCondition ref="A2:A11"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Day 01.xlsx
+++ b/Day 01.xlsx
@@ -9,17 +9,23 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Lesson 01" sheetId="1" r:id="rId1"/>
-    <sheet name="Lesson 02" sheetId="2" r:id="rId2"/>
-    <sheet name="Lesson 07" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet8" sheetId="9" r:id="rId5"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Lesson 07'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <pivotCaches>
+    <pivotCache cacheId="6" r:id="rId7"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="70">
   <si>
     <t>Alex</t>
   </si>
@@ -37,9 +43,6 @@
     <t>Islamabad</t>
   </si>
   <si>
-    <t>Day</t>
-  </si>
-  <si>
     <t>Sales (Rs.)</t>
   </si>
   <si>
@@ -79,9 +82,6 @@
     <t>Count of Day Names</t>
   </si>
   <si>
-    <t>Performance</t>
-  </si>
-  <si>
     <t>My Shop Sales Report — Week 1</t>
   </si>
   <si>
@@ -128,6 +128,123 @@
   </si>
   <si>
     <t>Bakery</t>
+  </si>
+  <si>
+    <t>Student ID</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>S002</t>
+  </si>
+  <si>
+    <t>S003</t>
+  </si>
+  <si>
+    <t>S004</t>
+  </si>
+  <si>
+    <t>S005</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>Ali</t>
+  </si>
+  <si>
+    <t>Fatima</t>
+  </si>
+  <si>
+    <t>Usman</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>Hamza</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Incomplete</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>Arts</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Commerce</t>
+  </si>
+  <si>
+    <t>Salesperson</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Lahore</t>
+  </si>
+  <si>
+    <t>Karachi</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Sales</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>(All)</t>
   </si>
 </sst>
 </file>
@@ -145,7 +262,7 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -153,32 +270,25 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -195,6 +305,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -263,25 +391,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -297,6 +431,3199 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Daily Sales Report</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2750</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B4CA-46E6-9E0E-A06370D21538}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="927336351"/>
+        <c:axId val="927333439"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="927336351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927333439"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="927333439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927336351"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Sales Trend This Week</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2750</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9131-45F6-8173-A50122FB2064}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="927336767"/>
+        <c:axId val="927338847"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="927336767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927338847"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="927338847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927336767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Sales by Category</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4BAC-4C8E-A144-4E47FD5F88E3}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4BAC-4C8E-A144-4E47FD5F88E3}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet3!$B$1:$C$31</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="2"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1200</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>3200</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2100</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>3800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>650</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>950</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2700</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1500</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1200</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>3200</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2100</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>3800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>650</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>950</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2700</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1500</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1200</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>3200</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2100</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>3800</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>650</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Dairy</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>950</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Bakery</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2700</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1500</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Fruit</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Sales (Rs.)</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Category</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Sheet3!$B$31,Sheet3!$C$31)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-188B-4573-B7D2-8432645E3937}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>168275</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>146049</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>22224</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="umer" refreshedDate="46117.668395833331" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="12">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D13" sheet="Sheet5"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Salesperson" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Ahmed"/>
+        <s v="Sara"/>
+        <s v="Ali"/>
+        <s v="Fatima"/>
+        <s v="Usman"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Lahore"/>
+        <s v="Karachi"/>
+        <s v="Islamabad"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Apples"/>
+        <s v="Mangoes"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1600" maxValue="4200"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="12">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2500"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="3800"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1900"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="4200"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="2100"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="3300"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="2900"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="3500"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2700"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1600"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="4100"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,7 +3919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -602,154 +3929,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
-      <c r="A1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="B2" s="3">
         <v>3000</v>
       </c>
-      <c r="C3" s="4" t="str">
-        <f>IF(B3&gt;2000,"Good Day","Bad Day")</f>
+      <c r="C2" s="3" t="str">
+        <f t="shared" ref="C2:C7" si="0">IF(B2&gt;2000,"Good Day","Bad Day")</f>
         <v>Good Day</v>
       </c>
-      <c r="D3">
+      <c r="D2">
         <f>100+200</f>
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
         <v>2300</v>
       </c>
-      <c r="C4" s="2" t="str">
-        <f>IF(B4&gt;2000,"Good Day","Bad Day")</f>
+      <c r="C3" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>Good Day</v>
       </c>
-      <c r="D4">
+      <c r="D3">
         <f>500-150</f>
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
         <v>1800</v>
       </c>
-      <c r="C5" s="4" t="str">
-        <f>IF(B5&gt;2000,"Good Day","Bad Day")</f>
+      <c r="C4" s="3" t="str">
+        <f t="shared" si="0"/>
         <v>Bad Day</v>
       </c>
-      <c r="D5">
+      <c r="D4">
         <f>50*4</f>
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
         <v>3100</v>
       </c>
-      <c r="C6" s="2" t="str">
-        <f>IF(B6&gt;2000,"Good Day","Bad Day")</f>
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>Good Day</v>
       </c>
-      <c r="D6">
+      <c r="D5">
         <f>100/4</f>
         <v>25</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2750</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Good Day</v>
+      </c>
+    </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4">
-        <v>2750</v>
-      </c>
-      <c r="C7" s="4" t="str">
-        <f>IF(B7&gt;2000,"Good Day","Bad Day")</f>
+      <c r="B7" s="2">
+        <v>4200</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f t="shared" si="0"/>
         <v>Good Day</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="5">
+        <f>SUM(B2:B7)</f>
+        <v>17150</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5">
+        <f>AVERAGE(B2:B7)</f>
+        <v>2858.3333333333335</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5">
+        <f>MAX(B2:B7)</f>
         <v>4200</v>
       </c>
-      <c r="C8" s="2" t="str">
-        <f>IF(B8&gt;2000,"Good Day","Bad Day")</f>
-        <v>Good Day</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="9">
-        <f>SUM(B3:B8)</f>
-        <v>17150</v>
-      </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="9">
-        <f>AVERAGE(B3:B8)</f>
-        <v>2858.3333333333335</v>
-      </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="9">
-        <f>MAX(B3:B8)</f>
-        <v>4200</v>
+      <c r="B11" s="5">
+        <f>MIN(B2:B7)</f>
+        <v>1800</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="9">
-        <f>MIN(B3:B8)</f>
-        <v>1800</v>
-      </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
+      <c r="B13" s="2">
+        <f>COUNT(B2:B7)</f>
+        <v>6</v>
+      </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -757,20 +4083,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <f>COUNT(B3:B8)</f>
+        <f>COUNTA(A2:A7)</f>
         <v>6</v>
       </c>
       <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2">
-        <f>COUNTA(A3:A8)</f>
-        <v>6</v>
-      </c>
-      <c r="C15" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -778,6 +4094,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -792,344 +4109,344 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="10">
+      <c r="B2" s="6">
         <v>1500</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>30</v>
+      <c r="C2" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2">
         <v>2700</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="6">
+        <v>950</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="10">
-        <v>950</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2">
         <v>650</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="10">
+      <c r="A6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="6">
         <v>3800</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>32</v>
+      <c r="C6" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2">
         <v>2100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="10">
+      <c r="A8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6">
         <v>1800</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>32</v>
+      <c r="C8" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
         <v>3200</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="10">
+      <c r="A10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
         <v>800</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>31</v>
+      <c r="C10" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2">
         <v>1200</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>31</v>
+      <c r="C11" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="10">
+      <c r="A12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="6">
         <v>1500</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>30</v>
+      <c r="C12" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2">
         <v>2700</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="6">
+        <v>950</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="10">
-        <v>950</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2">
         <v>650</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="10">
+      <c r="A16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="6">
         <v>3800</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>32</v>
+      <c r="C16" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B17" s="2">
         <v>2100</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="10">
+      <c r="A18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="6">
         <v>1800</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>32</v>
+      <c r="C18" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2">
         <v>3200</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="10">
+      <c r="A20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="6">
         <v>800</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>31</v>
+      <c r="C20" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2">
         <v>1200</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>31</v>
+      <c r="C21" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="10">
+      <c r="A22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6">
         <v>1500</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>30</v>
+      <c r="C22" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2">
         <v>2700</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="6">
+        <v>950</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="10">
-        <v>950</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2">
         <v>650</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="10">
+      <c r="A26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6">
         <v>3800</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>32</v>
+      <c r="C26" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B27" s="2">
         <v>2100</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="10">
+      <c r="A28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6">
         <v>1800</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>32</v>
+      <c r="C28" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B29" s="2">
         <v>3200</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="10">
+      <c r="A30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="6">
         <v>800</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>31</v>
+      <c r="C30" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2">
         <v>1200</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>31</v>
+      <c r="C31" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1138,5 +4455,523 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="12">
+        <v>85</v>
+      </c>
+      <c r="C2" s="12" t="str">
+        <f>VLOOKUP(A2,$J$2:$L$6,2,0)</f>
+        <v>Ahmed</v>
+      </c>
+      <c r="D2" s="12" t="str">
+        <f>VLOOKUP(A2,$J$2:$L$6,3,0)</f>
+        <v>A</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f>VLOOKUP(A3,$J$2:$L$6,2,0)</f>
+        <v>Sara</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>VLOOKUP(A3,$J$2:$L$6,3,0)</f>
+        <v>B</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="12">
+        <v>91</v>
+      </c>
+      <c r="C4" s="12" t="str">
+        <f>VLOOKUP(A4,$J$2:$L$6,2,0)</f>
+        <v>Hamza</v>
+      </c>
+      <c r="D4" s="12" t="str">
+        <f>VLOOKUP(A4,$J$2:$L$6,3,0)</f>
+        <v>A+</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2">
+        <v>68</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f>VLOOKUP(A5,$J$2:$L$6,2,0)</f>
+        <v>Fatima</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f>VLOOKUP(A5,$J$2:$L$6,3,0)</f>
+        <v>C</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="12">
+        <v>78</v>
+      </c>
+      <c r="C6" s="12" t="str">
+        <f>VLOOKUP(A6,$J$2:$L$6,2,0)</f>
+        <v>Usman</v>
+      </c>
+      <c r="D6" s="12" t="str">
+        <f>VLOOKUP(A6,$J$2:$L$6,3,0)</f>
+        <v>B+</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6">
+      <formula1>"Pass,Fail,Incomplete"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Marks!" error="Marks must be between 0 and 100!" sqref="B2:B6">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6">
+      <formula1>"Science,Arts,Commerce,Engineering"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15">
+        <v>5400</v>
+      </c>
+      <c r="C5" s="15">
+        <v>7400</v>
+      </c>
+      <c r="D5" s="15">
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="15">
+        <v>4300</v>
+      </c>
+      <c r="C6" s="15">
+        <v>6900</v>
+      </c>
+      <c r="D6" s="15">
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="15">
+        <v>3700</v>
+      </c>
+      <c r="C7" s="15">
+        <v>6700</v>
+      </c>
+      <c r="D7" s="15">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="15">
+        <v>13400</v>
+      </c>
+      <c r="C8" s="15">
+        <v>21000</v>
+      </c>
+      <c r="D8" s="15">
+        <v>34400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="12">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="12">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="12">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="12">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="12">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Day 01.xlsx
+++ b/Day 01.xlsx
@@ -9,22 +9,24 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet8" sheetId="9" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="9" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="11" r:id="rId7"/>
+    <sheet name="Sheet8" sheetId="12" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId7"/>
+    <pivotCache cacheId="5" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="87">
   <si>
     <t>Alex</t>
   </si>
@@ -245,6 +247,57 @@
   </si>
   <si>
     <t>(All)</t>
+  </si>
+  <si>
+    <t>Bilal</t>
+  </si>
+  <si>
+    <t>Ayesha</t>
+  </si>
+  <si>
+    <t>Peshawar</t>
+  </si>
+  <si>
+    <t>Attendance(%)</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>City Type</t>
+  </si>
+  <si>
+    <t>Top Performer</t>
+  </si>
+  <si>
+    <t>ahmed khan</t>
+  </si>
+  <si>
+    <t>SARA ALI</t>
+  </si>
+  <si>
+    <t>AYESHA KHAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  bilal ahmed</t>
+  </si>
+  <si>
+    <t>lahore</t>
+  </si>
+  <si>
+    <t>islamabad</t>
+  </si>
+  <si>
+    <t>Clean Name</t>
+  </si>
+  <si>
+    <t>Clean City</t>
+  </si>
+  <si>
+    <t>Trimmed Name</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
 </sst>
 </file>
@@ -283,7 +336,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -323,6 +376,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -400,6 +459,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -409,13 +475,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,7 +534,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -564,7 +623,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -849,7 +907,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -940,7 +997,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1225,7 +1281,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1601,7 +1656,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3424,7 +3478,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="umer" refreshedDate="46117.668395833331" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="12">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="umer" refreshedDate="46117.881428125002" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="12">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D13" sheet="Sheet5"/>
   </cacheSource>
@@ -3541,7 +3595,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -3929,11 +3983,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -4475,62 +4529,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="9">
         <v>85</v>
       </c>
-      <c r="C2" s="12" t="str">
+      <c r="C2" s="9" t="str">
         <f>VLOOKUP(A2,$J$2:$L$6,2,0)</f>
         <v>Ahmed</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="9" t="str">
         <f>VLOOKUP(A2,$J$2:$L$6,3,0)</f>
         <v>A</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="9" t="s">
         <v>45</v>
       </c>
     </row>
@@ -4566,33 +4620,33 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="9">
         <v>91</v>
       </c>
-      <c r="C4" s="12" t="str">
+      <c r="C4" s="9" t="str">
         <f>VLOOKUP(A4,$J$2:$L$6,2,0)</f>
         <v>Hamza</v>
       </c>
-      <c r="D4" s="12" t="str">
+      <c r="D4" s="9" t="str">
         <f>VLOOKUP(A4,$J$2:$L$6,3,0)</f>
         <v>A+</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="9" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4628,33 +4682,33 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="9">
         <v>78</v>
       </c>
-      <c r="C6" s="12" t="str">
+      <c r="C6" s="9" t="str">
         <f>VLOOKUP(A6,$J$2:$L$6,2,0)</f>
         <v>Usman</v>
       </c>
-      <c r="D6" s="12" t="str">
+      <c r="D6" s="9" t="str">
         <f>VLOOKUP(A6,$J$2:$L$6,3,0)</f>
         <v>B+</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="9" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4678,6 +4732,204 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="9">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="9">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="9">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4688,7 +4940,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B1" t="s">
@@ -4696,15 +4948,15 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B4" t="s">
@@ -4718,59 +4970,310 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="12">
         <v>5400</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="12">
         <v>7400</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="12">
         <v>12800</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="12">
         <v>4300</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="12">
         <v>6900</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="12">
         <v>11200</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="12">
         <v>3700</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="12">
         <v>6700</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="12">
         <v>10400</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="12">
         <v>13400</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="12">
         <v>21000</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="12">
         <v>34400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="9">
+        <v>3500</v>
+      </c>
+      <c r="C2" s="9">
+        <v>95</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="9" t="str">
+        <f>IF(AND(B2&gt;2500,C2&gt;90),"Yes - Bonus!","No Bonus")</f>
+        <v>Yes - Bonus!</v>
+      </c>
+      <c r="F2" s="9" t="str">
+        <f>IF(OR(D2="Lahore",D2="Karachi"),"Major City","Other City")</f>
+        <v>Major City</v>
+      </c>
+      <c r="G2" s="9" t="str">
+        <f>IF(AND(B2&gt;3000,C2&gt;90,D2="Lahore"),"Star!","Regular")</f>
+        <v>Star!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2800</v>
+      </c>
+      <c r="C3" s="2">
+        <v>88</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <f t="shared" ref="E3:E9" si="0">IF(AND(B3&gt;2500,C3&gt;90),"Yes - Bonus!","No Bonus")</f>
+        <v>No Bonus</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <f t="shared" ref="F3:F9" si="1">IF(OR(D3="Lahore",D3="Karachi"),"Major City","Other City")</f>
+        <v>Major City</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <f t="shared" ref="G3:G9" si="2">IF(AND(B3&gt;3000,C3&gt;90,D3="Lahore"),"Star!","Regular")</f>
+        <v>Regular</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="9">
+        <v>4200</v>
+      </c>
+      <c r="C4" s="9">
+        <v>92</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes - Bonus!</v>
+      </c>
+      <c r="F4" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Other City</v>
+      </c>
+      <c r="G4" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Regular</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3100</v>
+      </c>
+      <c r="C5" s="2">
+        <v>78</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Major City</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Regular</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="9">
+        <v>2500</v>
+      </c>
+      <c r="C6" s="9">
+        <v>96</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+      <c r="F6" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Other City</v>
+      </c>
+      <c r="G6" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Regular</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C7" s="2">
+        <v>85</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Major City</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Regular</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="9">
+        <v>4500</v>
+      </c>
+      <c r="C8" s="9">
+        <v>91</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes - Bonus!</v>
+      </c>
+      <c r="F8" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Major City</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Star!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2200</v>
+      </c>
+      <c r="C9" s="2">
+        <v>94</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Other City</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Regular</v>
       </c>
     </row>
   </sheetData>
@@ -4778,197 +5281,221 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="12">
+      <c r="D1" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="16">
         <v>2500</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D2" s="16" t="str">
+        <f>PROPER(A2)</f>
+        <v>Ahmed Khan</v>
+      </c>
+      <c r="E2" s="16" t="str">
+        <f>PROPER(B2)</f>
+        <v>Lahore</v>
+      </c>
+      <c r="F2" s="16" t="str">
+        <f>TRIM(PROPER(A2))</f>
+        <v>Ahmed Khan</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C3" s="2">
         <v>3800</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="D3" s="2" t="str">
+        <f t="shared" ref="D3:D9" si="0">PROPER(A3)</f>
+        <v>Sara Ali</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f t="shared" ref="E3:E9" si="1">PROPER(B3)</f>
+        <v>Karachi</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <f t="shared" ref="F3:F9" si="2">TRIM(PROPER(A3))</f>
+        <v>Sara Ali</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="C4" s="16">
         <v>1900</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D4" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Unknown</v>
+      </c>
+      <c r="E4" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Islamabad</v>
+      </c>
+      <c r="F4" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2">
+        <v>81</v>
+      </c>
+      <c r="C5" s="2">
         <v>4200</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Unknown</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Lahore</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C6" s="16">
         <v>2100</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D6" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Unknown</v>
+      </c>
+      <c r="E6" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Karachi</v>
+      </c>
+      <c r="F6" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2">
+        <v>81</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2500</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Unknown</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Lahore</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="16">
         <v>3300</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="12">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D8" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>Ayesha Khan</v>
+      </c>
+      <c r="E8" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v>Islamabad</v>
+      </c>
+      <c r="F8" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>Ayesha Khan</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="C9" s="2">
         <v>2900</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="12">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="12">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="2">
-        <v>4100</v>
+      <c r="D9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  Bilal Ahmed</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Karachi</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Bilal Ahmed</v>
       </c>
     </row>
   </sheetData>
